--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\PycharmProjects\BPVis_LT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DFAB7A-8698-4C8A-9AE2-149ADB686500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3B85E1B-924C-45FB-8751-7A65585D1D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-2895" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25905" yWindow="-2775" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>email</t>
   </si>
@@ -32,13 +32,55 @@
   </si>
   <si>
     <t>A+b=1234</t>
+  </si>
+  <si>
+    <t>joao.mata@wernersobek.com</t>
+  </si>
+  <si>
+    <t>christian.boesselmann@wernersobek.com</t>
+  </si>
+  <si>
+    <t>priji.balakrishnan@wernersobek.com</t>
+  </si>
+  <si>
+    <t>elias.hartung@wernersobek.com</t>
+  </si>
+  <si>
+    <t>roberto.huebner@wernersobek.com</t>
+  </si>
+  <si>
+    <t>sebastian.janusz@wernersobek.com</t>
+  </si>
+  <si>
+    <t>michelle.kahn@wernersobek.com</t>
+  </si>
+  <si>
+    <t>lara.katscher@wernersobek.com</t>
+  </si>
+  <si>
+    <t>ongun.kazanci@wernersobek.com</t>
+  </si>
+  <si>
+    <t>baptiste.lach@wernersobek.com</t>
+  </si>
+  <si>
+    <t>oliver.piepka@wernersobek.com</t>
+  </si>
+  <si>
+    <t>sven.simon@wernersobek.com</t>
+  </si>
+  <si>
+    <t>florian.starz@wernersobek.com</t>
+  </si>
+  <si>
+    <t>stefanie.weidner@wernersobek.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -57,6 +99,10 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -261,7 +307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -284,9 +330,123 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{520160CC-0C3A-4DED-863E-7D37551E7E34}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{701536B6-39BD-4C30-A9ED-F936F20F51E7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\PycharmProjects\BPVis_LT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3B85E1B-924C-45FB-8751-7A65585D1D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4E30EA-02B4-4201-84DA-6653B9B53878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25905" yWindow="-2775" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-76920" yWindow="3465" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <t>email</t>
   </si>
@@ -74,21 +87,54 @@
   </si>
   <si>
     <t>stefanie.weidner@wernersobek.com</t>
+  </si>
+  <si>
+    <t>expiration_date</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>Required columns</t>
+  </si>
+  <si>
+    <t>email, password, expiration_date</t>
+  </si>
+  <si>
+    <t>Expiration rule</t>
+  </si>
+  <si>
+    <t>Access is allowed until the expiration date inclusive; denied after it.</t>
+  </si>
+  <si>
+    <t>No expiration</t>
+  </si>
+  <si>
+    <t>Leave expiration_date empty.</t>
+  </si>
+  <si>
+    <t>Date format</t>
+  </si>
+  <si>
+    <t>Use yyyy-mm-dd where possible.</t>
+  </si>
+  <si>
+    <t>Password comparison</t>
+  </si>
+  <si>
+    <t>Passwords are case-sensitive.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -105,6 +151,17 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -115,7 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0F766E"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,15 +188,19 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -307,143 +369,231 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="C2" s="2">
+        <v>73050</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="2">
+        <v>73050</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" s="2">
+        <v>73050</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" s="2">
+        <v>73050</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" s="2">
+        <v>73050</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15" s="2">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
       </c>
+      <c r="C16" s="2">
+        <v>73050</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <mergeCells count="1">
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{520160CC-0C3A-4DED-863E-7D37551E7E34}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{701536B6-39BD-4C30-A9ED-F936F20F51E7}"/>

--- a/users.xlsx
+++ b/users.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\PycharmProjects\BPVis_LT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4E30EA-02B4-4201-84DA-6653B9B53878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD0B2E95-F79C-4AA8-B089-4C71DD08BA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-76920" yWindow="3465" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25905" yWindow="-2775" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>email</t>
   </si>
@@ -41,24 +28,57 @@
     <t>password</t>
   </si>
   <si>
+    <t>expiration_date</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
     <t>rodrigo.carvalho@wernersobek.com</t>
   </si>
   <si>
     <t>A+b=1234</t>
   </si>
   <si>
+    <t>Required columns</t>
+  </si>
+  <si>
     <t>joao.mata@wernersobek.com</t>
   </si>
   <si>
+    <t>Expiration rule</t>
+  </si>
+  <si>
+    <t>Access is allowed until the expiration date inclusive; denied after it.</t>
+  </si>
+  <si>
     <t>christian.boesselmann@wernersobek.com</t>
   </si>
   <si>
+    <t>No expiration</t>
+  </si>
+  <si>
+    <t>Leave expiration_date empty.</t>
+  </si>
+  <si>
     <t>priji.balakrishnan@wernersobek.com</t>
   </si>
   <si>
+    <t>Date format</t>
+  </si>
+  <si>
+    <t>Use yyyy-mm-dd where possible.</t>
+  </si>
+  <si>
     <t>elias.hartung@wernersobek.com</t>
   </si>
   <si>
+    <t>Password comparison</t>
+  </si>
+  <si>
+    <t>Passwords are case-sensitive.</t>
+  </si>
+  <si>
     <t>roberto.huebner@wernersobek.com</t>
   </si>
   <si>
@@ -89,40 +109,40 @@
     <t>stefanie.weidner@wernersobek.com</t>
   </si>
   <si>
-    <t>expiration_date</t>
-  </si>
-  <si>
-    <t>Instructions</t>
-  </si>
-  <si>
-    <t>Required columns</t>
-  </si>
-  <si>
-    <t>email, password, expiration_date</t>
-  </si>
-  <si>
-    <t>Expiration rule</t>
-  </si>
-  <si>
-    <t>Access is allowed until the expiration date inclusive; denied after it.</t>
-  </si>
-  <si>
-    <t>No expiration</t>
-  </si>
-  <si>
-    <t>Leave expiration_date empty.</t>
-  </si>
-  <si>
-    <t>Date format</t>
-  </si>
-  <si>
-    <t>Use yyyy-mm-dd where possible.</t>
-  </si>
-  <si>
-    <t>Password comparison</t>
-  </si>
-  <si>
-    <t>Passwords are case-sensitive.</t>
+    <t>access_mode</t>
+  </si>
+  <si>
+    <t>edit mode</t>
+  </si>
+  <si>
+    <t>email, password, expiration_date, access_mode</t>
+  </si>
+  <si>
+    <t>Access mode</t>
+  </si>
+  <si>
+    <t>Use either edit mode or viewer mode.</t>
+  </si>
+  <si>
+    <t>Edit mode</t>
+  </si>
+  <si>
+    <t>All application features are available.</t>
+  </si>
+  <si>
+    <t>Viewer mode</t>
+  </si>
+  <si>
+    <t>Only the Viewer Mode permissions defined in BPVis are available.</t>
+  </si>
+  <si>
+    <t>viewer mode</t>
+  </si>
+  <si>
+    <t>d.maclennan@maxfordham.com</t>
+  </si>
+  <si>
+    <t>MF_HSO</t>
   </si>
 </sst>
 </file>
@@ -132,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -142,13 +162,8 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -173,7 +188,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -195,16 +209,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Link" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Link" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -263,9 +277,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -369,12 +383,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -386,217 +401,301 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2">
         <v>73050</v>
       </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2">
         <v>73050</v>
       </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2">
         <v>73050</v>
       </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>73050</v>
       </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>73050</v>
       </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
         <v>73050</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2">
         <v>73050</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2">
         <v>73050</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2">
         <v>73050</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2">
         <v>73050</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2">
         <v>73050</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2">
         <v>73050</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2">
         <v>73050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2">
         <v>73050</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>73050</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="D2:D100" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"edit mode,viewer mode"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{520160CC-0C3A-4DED-863E-7D37551E7E34}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{701536B6-39BD-4C30-A9ED-F936F20F51E7}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A17" r:id="rId3" xr:uid="{6B9AB63E-B86F-41F6-9DED-B4D6D0299F24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD0B2E95-F79C-4AA8-B089-4C71DD08BA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7A689D-51A5-4DF0-9F26-DFC25B9E3305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25905" yWindow="-2775" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-48240" yWindow="585" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
   <si>
     <t>email</t>
   </si>
@@ -31,19 +31,70 @@
     <t>expiration_date</t>
   </si>
   <si>
+    <t>rodrigo.carvalho@wernersobek.com</t>
+  </si>
+  <si>
+    <t>A+b=1234</t>
+  </si>
+  <si>
+    <t>joao.mata@wernersobek.com</t>
+  </si>
+  <si>
+    <t>christian.boesselmann@wernersobek.com</t>
+  </si>
+  <si>
+    <t>priji.balakrishnan@wernersobek.com</t>
+  </si>
+  <si>
+    <t>elias.hartung@wernersobek.com</t>
+  </si>
+  <si>
+    <t>roberto.huebner@wernersobek.com</t>
+  </si>
+  <si>
+    <t>sebastian.janusz@wernersobek.com</t>
+  </si>
+  <si>
+    <t>michelle.kahn@wernersobek.com</t>
+  </si>
+  <si>
+    <t>lara.katscher@wernersobek.com</t>
+  </si>
+  <si>
+    <t>ongun.kazanci@wernersobek.com</t>
+  </si>
+  <si>
+    <t>baptiste.lach@wernersobek.com</t>
+  </si>
+  <si>
+    <t>oliver.piepka@wernersobek.com</t>
+  </si>
+  <si>
+    <t>sven.simon@wernersobek.com</t>
+  </si>
+  <si>
+    <t>florian.starz@wernersobek.com</t>
+  </si>
+  <si>
+    <t>stefanie.weidner@wernersobek.com</t>
+  </si>
+  <si>
+    <t>access_mode</t>
+  </si>
+  <si>
+    <t>data_source_file</t>
+  </si>
+  <si>
     <t>Instructions</t>
   </si>
   <si>
-    <t>rodrigo.carvalho@wernersobek.com</t>
-  </si>
-  <si>
-    <t>A+b=1234</t>
+    <t>edit mode</t>
   </si>
   <si>
     <t>Required columns</t>
   </si>
   <si>
-    <t>joao.mata@wernersobek.com</t>
+    <t>email, password, expiration_date, access_mode, data_source_file</t>
   </si>
   <si>
     <t>Expiration rule</t>
@@ -52,72 +103,24 @@
     <t>Access is allowed until the expiration date inclusive; denied after it.</t>
   </si>
   <si>
-    <t>christian.boesselmann@wernersobek.com</t>
-  </si>
-  <si>
     <t>No expiration</t>
   </si>
   <si>
     <t>Leave expiration_date empty.</t>
   </si>
   <si>
-    <t>priji.balakrishnan@wernersobek.com</t>
-  </si>
-  <si>
     <t>Date format</t>
   </si>
   <si>
     <t>Use yyyy-mm-dd where possible.</t>
   </si>
   <si>
-    <t>elias.hartung@wernersobek.com</t>
-  </si>
-  <si>
     <t>Password comparison</t>
   </si>
   <si>
     <t>Passwords are case-sensitive.</t>
   </si>
   <si>
-    <t>roberto.huebner@wernersobek.com</t>
-  </si>
-  <si>
-    <t>sebastian.janusz@wernersobek.com</t>
-  </si>
-  <si>
-    <t>michelle.kahn@wernersobek.com</t>
-  </si>
-  <si>
-    <t>lara.katscher@wernersobek.com</t>
-  </si>
-  <si>
-    <t>ongun.kazanci@wernersobek.com</t>
-  </si>
-  <si>
-    <t>baptiste.lach@wernersobek.com</t>
-  </si>
-  <si>
-    <t>oliver.piepka@wernersobek.com</t>
-  </si>
-  <si>
-    <t>sven.simon@wernersobek.com</t>
-  </si>
-  <si>
-    <t>florian.starz@wernersobek.com</t>
-  </si>
-  <si>
-    <t>stefanie.weidner@wernersobek.com</t>
-  </si>
-  <si>
-    <t>access_mode</t>
-  </si>
-  <si>
-    <t>edit mode</t>
-  </si>
-  <si>
-    <t>email, password, expiration_date, access_mode</t>
-  </si>
-  <si>
     <t>Access mode</t>
   </si>
   <si>
@@ -127,22 +130,31 @@
     <t>Edit mode</t>
   </si>
   <si>
-    <t>All application features are available.</t>
+    <t>All application features are available. data_source_file may be left empty.</t>
   </si>
   <si>
     <t>Viewer mode</t>
   </si>
   <si>
-    <t>Only the Viewer Mode permissions defined in BPVis are available.</t>
-  </si>
-  <si>
-    <t>viewer mode</t>
-  </si>
-  <si>
-    <t>d.maclennan@maxfordham.com</t>
+    <t>The assigned project is loaded automatically; the user does not upload the workbook.</t>
+  </si>
+  <si>
+    <t>Data source file</t>
+  </si>
+  <si>
+    <t>For viewer mode, enter the exact .xlsx filename stored directly in the app's External folder.</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Use a filename only (for example Project_A.xlsx), not a folder path or URL.</t>
   </si>
   <si>
     <t>MF_HSO</t>
+  </si>
+  <si>
+    <t>HSO_ENE_LPH2-00.xlsx</t>
   </si>
 </sst>
 </file>
@@ -205,7 +217,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -213,8 +225,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -383,17 +400,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -404,283 +423,311 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="G5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="28">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>73050</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>73050</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2">
         <v>46387</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -688,14 +735,13 @@
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D100" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D2:D16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"edit mode,viewer mode"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A17" r:id="rId3" xr:uid="{6B9AB63E-B86F-41F6-9DED-B4D6D0299F24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7A689D-51A5-4DF0-9F26-DFC25B9E3305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72CA9279-8D04-4A4A-857F-D8EDB9AE69E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-48240" yWindow="585" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34935" yWindow="375" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
   <si>
     <t>email</t>
   </si>
@@ -155,6 +155,18 @@
   </si>
   <si>
     <t>HSO_ENE_LPH2-00.xlsx</t>
+  </si>
+  <si>
+    <t>WS_HEI_HOT</t>
+  </si>
+  <si>
+    <t>HEI_HOT_LPH3_ENE-00.xlsx</t>
+  </si>
+  <si>
+    <t>WS_HEI_OFC</t>
+  </si>
+  <si>
+    <t>HEI_OFC_LPH3_ENE-00.xlsx</t>
   </si>
 </sst>
 </file>
@@ -400,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -728,6 +740,40 @@
       </c>
       <c r="E17" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
